--- a/光伏配储项目/电价数据/2026/高明站.xlsx
+++ b/光伏配储项目/电价数据/2026/高明站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5106700000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.78211</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.58666</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.6124700000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5202</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.5136799999999999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43752</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45435</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44109</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42329</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42059</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40883</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42305</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41248</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39141</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41687</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42068</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41383</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42383</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44406</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.24028</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12791</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10383</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11803</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.10633</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13025</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.07836</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.14952</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.19749</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.14424</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.01639</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09121</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.12083</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.04301</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.1787</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.22745</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.18722</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23904</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.08567</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.00656</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.14086</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.20406</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.2820299999999999</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.20756</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.43459</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.70601</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5057</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.56616</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.31727</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.42554</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.65324</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.49996</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42028</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57972</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47611</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6369199999999999</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.8244400000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.64786</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.79632</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.14523</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.44469</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6897300000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58717</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.8128500000000001</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.6075499999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.60314</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.65274</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6246</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47843</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47782</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41596</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42562</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7079500000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.54958</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.75947</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.34943</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.80674</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.52859</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5187999999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50519</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51076</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.4892</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4191</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.50004</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59735</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.70148</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4298</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.42552</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.43203</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5225700000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.21912</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.06656000000000001</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.47196</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.4731</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.45812</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.47616</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.43703</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.47098</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5219199999999999</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7413200000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.27841</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.39482</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.5928099999999999</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.01125</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.52289</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.14226</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.43353</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.47909</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.5159199999999999</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.5079900000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.46861</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.44174</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.43455</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.62313</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.75707</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.6163999999999999</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.70386</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7664500000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.73939</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.6327999999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.5681</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7579600000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.57613</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.5412</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.00363</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.46695</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.57278</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.46923</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.46246</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.47924</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.43701</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.39492</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33455</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5129600000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.84804</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42297</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.5574600000000001</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38998</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.40573</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.46239</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.48208</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47381</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.48099</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.47513</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.41853</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.38346</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1.10134</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.7575599999999999</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.79667</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.21822</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>1.27661</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26796</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47978</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.42855</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.52691</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.49204</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.42917</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.17023</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.28458</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40278</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.42958</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.43279</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.40204</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5637000000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.63919</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.71184</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.46916</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.49692</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42664</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5275599999999999</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.42551</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.47762</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.45187</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.47275</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.45879</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.41718</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.44071</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.41814</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.40574</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41047</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34241</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.36438</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.2291</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.25384</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.47419</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.48838</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.57016</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.47395</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.5908</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.47723</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.14531</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.09665</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.27676</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.44033</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.25813</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.29644</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.75581</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.07232999999999999</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.1954</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.26145</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.26642</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.23269</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.24813</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.21874</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.13169</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.28307</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.39297</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.43017</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.6141799999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.4685</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.44955</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.2997</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.40681</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29458</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29203</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27907</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.2601</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.11576</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04385</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.11349</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.12713</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04457</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04568</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.08062000000000001</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04654</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03446</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04686999999999999</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04844</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04277</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.0429</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04243</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04245</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04255</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04207</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04256</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04541</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04504</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04188</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04169</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04312</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.0457</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04531</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04927</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.2185</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04509000000000001</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05117</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05594</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.0366</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.01913</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.22446</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.12827</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.17159</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38746</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41689</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35085</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.75446</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44611</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42322</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10255</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04371</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.0469</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04532</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04547</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04381</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04384</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10311</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04472</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04355</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04378</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04564</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04545</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04313</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04324</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04325</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04516</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04406</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04381</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04565</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04448</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04953</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04725</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04763000000000001</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2001</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14299</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26908</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33565</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3179</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4047</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28825</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27119</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17257</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15881</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17112</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14786</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15959</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15876</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23642</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21418</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22673</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28596</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28127</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28072</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27185</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29603</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42799</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45461</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41801</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15637</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50773</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909400000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220800000000001</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78107</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.9205099999999999</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49465</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91608</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86787</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29933</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89288</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6326499999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19241</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8714500000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.54508</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33624</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03666</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53613</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7954600000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53027</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77749</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78111</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8773300000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87621</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49735</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40533</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45476</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21244</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87905</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55115</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62726</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5396799999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4992799999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45652</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42493</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43814</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45023</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.4528</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42015</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41478</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43377</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40407</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45084</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58648</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42769</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59599</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60236</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66838</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47344</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41918</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58163</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45242</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63464</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.9438799999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.92602</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86502</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44369</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.46678</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6281599999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41002</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41264</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45234</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35343</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.92426</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46693</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.42004</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47734</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38259</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40981</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38932</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49996</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16574</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26255</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19912</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27719</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19866</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27851</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2557</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4352200000000001</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.30739</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44837</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42038</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59657</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89039</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.37512</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.17478</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.71256</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.80765</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.66228</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.59041</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45547</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45512</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50748</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44466</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.4421</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41888</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42765</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50745</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43863</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41628</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43942</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39335</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.43229</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45549</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42766</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43861</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42764</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.42005</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40767</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5047200000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.38346</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.52883</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.89634</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.4936</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.54435</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25273</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.87697</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.14507</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.47968</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.46312</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.60693</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26432</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26278</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.29094</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.41194</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40379</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37147</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57938</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46708</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7885700000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.47065</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43723</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.4217</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32395</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42548</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28523</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.51871</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.48008</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.49381</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.46984</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.24098</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.24815</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.40227</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.25213</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.17704</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.23383</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.17701</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.23038</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.22463</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.42935</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.2203</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.18869</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.43073</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.23266</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.2393</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.46224</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.42093</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.42874</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.44764</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.47655</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.46548</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.63405</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.4034</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38641</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4528</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39541</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40305</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44686</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.4428</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4421</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44719</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44754</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40437</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39263</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34876</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5460900000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47382</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42737</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41918</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37182</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38197</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39553</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39403</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38279</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38278</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29615</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26457</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20034</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30739</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24872</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24149</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26851</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28327</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.25194</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24056</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.28924</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28401</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.22165</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.16052</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.25148</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.18308</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.24216</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.42059</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36813</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38158</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38185</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3868</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36121</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.40845</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38873</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37747</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.52316</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.43376</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.40428</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.44181</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.45074</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.06106</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.29249</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25007</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.40669</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.23111</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.26047</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.46354</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.4527</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7059500000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5182899999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.2619</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30843</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28685</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.48266</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27914</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38535</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40407</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34953</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38449</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42402</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64413</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7948200000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.44502</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46116</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34152</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.30183</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40758</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26437</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14174</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28476</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20072</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26162</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28019</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22333</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.27617</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28073</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29452</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14487</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43848</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38833</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40978</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.69717</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5921900000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.44296</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.41208</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6824199999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.77481</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.43292</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.4676</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40912</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47771</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43019</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37767</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35998</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49002</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5258400000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47718</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.4847</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41637</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39524</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40203</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40884</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40921</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39473</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41065</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.3898</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4218</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41742</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.4134</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45455</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44827</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5648200000000001</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5065</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45482</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.24938</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44567</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47671</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.43165</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.46421</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.46681</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.58041</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37748</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.42987</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.41327</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42152</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.65006</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.17183</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.39103</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42241</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.44274</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49864</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.44264</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50342</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.44892</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.61305</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.70451</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.7039500000000001</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.81043</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58377</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.51393</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.79876</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.74122</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62437</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66151</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44352</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47833</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.47422</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47733</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46076</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41769</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5514199999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42982</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44157</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.4513</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42685</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42172</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44202</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40992</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44967</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40436</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39195</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38651</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39727</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37303</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40275</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38384</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.21284</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39406</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40464</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45908</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39627</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46351</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11729</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18074</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.45395</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41665</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43005</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40875</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40821</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39504</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.3653</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44486</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39744</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39701</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37748</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.2794700000000001</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22737</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28792</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23071</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29076</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25056</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.26566</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.1398</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25383</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25121</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.30163</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17087</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18335</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22905</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26708</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23252</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27562</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28446</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28335</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37583</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35773</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38128</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36821</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35003</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30604</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.2512</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17189</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.21342</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.24662</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01839</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.0009599999999999999</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02588</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04907</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01242</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03904999999999999</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04909</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01082</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03641</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03265999999999999</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04719</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04658</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02314</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02231</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04913</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.15249</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04912</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0489</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00111</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04916</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04891</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04912</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03129</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04908</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04882</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04191</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18504</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20432</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2419</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28035</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26966</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27132</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.26917</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27503</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.4179</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30035</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.16093</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.6145900000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.41147</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.1889</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29068</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.26051</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.25181</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.27838</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.26459</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.23601</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.26392</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25518</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.29241</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27808</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.28354</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.26163</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28803</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28648</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.28715</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.24073</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.18565</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.67331</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.6673600000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.6829400000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.62386</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.18377</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11943</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.24658</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.19869</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.14158</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.14786</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.10708</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.23353</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.13169</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.04374</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.07063999999999999</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.12052</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.1874</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02314</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.14098</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.14989</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.1644</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.00852</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.12362</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.13454</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.13336</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.16812</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25879</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29571</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27965</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.44862</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37642</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36495</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3234</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.01648</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.56062</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.53449</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.41789</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.43417</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.45474</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.4391</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37951</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44623</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14177</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27884</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27021</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.28607</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.46316</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38307</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36822</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32732</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.57425</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.54714</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.49631</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.43718</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26312</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.27996</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41401</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40558</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.48277</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.49144</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.45347</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46904</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42401</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.58404</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.46325</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.41678</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.5829299999999999</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.42162</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36739</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.44458</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.39397</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39778</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38246</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.26318</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36439</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48115</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.44185</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.44182</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.44737</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.41335</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.46447</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.40436</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27491</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38454</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38603</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39633</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.49345</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.41169</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.46156</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.43941</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43481</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50343</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.56989</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.57077</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.44744</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.52877</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49812</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.53567</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.47383</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5202100000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.4783</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.5566599999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7828200000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5548999999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55855</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39201</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.43268</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.36953</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26426</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.24238</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27545</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17073</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.17764</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.07128</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.20769</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.03846</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.21682</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.17425</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.00726</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26458</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16912</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06338000000000001</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05604</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.07598000000000001</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.17396</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08377</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.0608</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15848</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.17799</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.29197</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.26231</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42485</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.42083</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42226</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39458</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38426</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.41932</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.42595</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38135</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.3742799999999999</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.26204</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36311</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.84737</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.47179</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.43274</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3864</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.27788</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.28796</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11654</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01249</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.009609999999999999</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03882</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.16432</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00544</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01884</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04606</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02022</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01144</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16312</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.27974</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04550999999999999</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.24836</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.17297</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.26985</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.49005</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41563</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40748</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39467</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.54737</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.26867</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37409</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40675</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39432</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37468</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36403</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.57875</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.4477</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37474</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28759</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.26722</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23891</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14888</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21565</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.23951</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.24349</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11896</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15758</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.02382</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.0259</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04719</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04721</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04573</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04626</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04456</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.08117000000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06444</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09991999999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.1789</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.20589</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12563</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.27082</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.24064</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12897</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05959</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26931</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.15416</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.12147</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.24358</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.19446</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.2505</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.25573</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.21241</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.25466</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.28628</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.28795</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40094</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4602</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37326</v>
       </c>
     </row>
   </sheetData>
